--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Nilesh\Python\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nilesh Yadav\Desktop\daily\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492651A0-742D-44AE-9513-97270D010A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EE641A-1283-40D3-85C9-673214022DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1248,20 +1248,22 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1020</v>
       </c>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nilesh Yadav\Desktop\daily\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EE641A-1283-40D3-85C9-673214022DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2ECC6F-C11D-47A9-94A7-CB892598C16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1247,27 +1253,47 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
+      <c r="A11" s="13">
+        <v>46262</v>
+      </c>
       <c r="B11" s="14">
         <v>420</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>180</v>
+      </c>
+      <c r="E11" s="14">
+        <v>120</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>120</v>
+      </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>420</v>
+        <v>1150</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>1020</v>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>290</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1287,9 +1313,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1309,9 +1341,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1331,9 +1369,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+      <c r="K14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1353,9 +1397,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+      <c r="K15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>67</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1375,9 +1425,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+      <c r="K16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1399,9 +1455,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1421,9 +1483,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+      <c r="K18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1443,9 +1511,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+      <c r="K19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1465,9 +1539,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1487,9 +1567,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+      <c r="K21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1509,9 +1595,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+      <c r="K22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1531,9 +1623,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+      <c r="K23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1553,9 +1651,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1575,9 +1679,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>67</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -1597,9 +1707,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -1619,9 +1735,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -1641,9 +1763,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nilesh Yadav\Desktop\daily\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2ECC6F-C11D-47A9-94A7-CB892598C16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8A08C3-EE79-47C3-86BF-CC957F56B8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,13 +237,13 @@
     <t>August</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>2026=09-11</t>
   </si>
 </sst>
 </file>
@@ -1297,21 +1297,37 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B12" s="14">
+        <v>500</v>
+      </c>
+      <c r="C12" s="14">
+        <v>80</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>80</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>120</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>540</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1325,21 +1341,37 @@
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B13" s="14">
+        <v>500</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>100</v>
+      </c>
+      <c r="E13" s="14">
+        <v>70</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>80</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>430</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1353,21 +1385,37 @@
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>70</v>
+      </c>
+      <c r="D14" s="14">
+        <v>230</v>
+      </c>
+      <c r="E14" s="14">
+        <v>50</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>6</v>
+      </c>
+      <c r="H14" s="14">
+        <v>70</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>300</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>60</v>
@@ -1381,21 +1429,37 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>40</v>
+      </c>
+      <c r="D15" s="14">
+        <v>200</v>
+      </c>
+      <c r="E15" s="14">
+        <v>80</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>50</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>650</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>60</v>
@@ -1404,32 +1468,48 @@
         <v>54</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>80</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>610</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
@@ -1437,23 +1517,37 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>200</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>60</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>500</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
@@ -1467,21 +1561,37 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>280</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>250</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="14">
+        <v>70</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>390</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>60</v>
@@ -1495,21 +1605,37 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B19" s="14">
+        <v>500</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>50</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>710</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>55</v>
@@ -1523,21 +1649,37 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B20" s="14">
+        <v>500</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14">
+        <v>180</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>120</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>610</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
@@ -1551,21 +1693,33 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B21" s="14">
+        <v>500</v>
+      </c>
+      <c r="C21" s="14">
+        <v>50</v>
+      </c>
+      <c r="D21" s="14">
+        <v>0</v>
+      </c>
+      <c r="E21" s="14">
+        <v>180</v>
+      </c>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="H21" s="14">
+        <v>40</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>670</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>57</v>
@@ -1579,21 +1733,33 @@
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="A22" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B22" s="14">
+        <v>380</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="H22" s="14">
+        <v>50</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>710</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>60</v>
@@ -1607,21 +1773,33 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="A23" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>200</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="H23" s="14">
+        <v>140</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>560</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>60</v>
@@ -1635,21 +1813,31 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="A24" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B24" s="14">
+        <v>450</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>150</v>
+      </c>
+      <c r="E24" s="14">
+        <v>80</v>
+      </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>710</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>730</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>49</v>
@@ -1663,21 +1851,31 @@
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
+      <c r="A25" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="14">
+        <v>380</v>
+      </c>
+      <c r="C25" s="14">
+        <v>70</v>
+      </c>
+      <c r="D25" s="14">
+        <v>140</v>
+      </c>
+      <c r="E25" s="14">
+        <v>90</v>
+      </c>
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>760</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
@@ -1686,26 +1884,36 @@
         <v>60</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="A26" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B26" s="14">
+        <v>520</v>
+      </c>
+      <c r="C26" s="14">
+        <v>50</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>80</v>
+      </c>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>670</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
@@ -1719,21 +1927,31 @@
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
+      <c r="A27" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B27" s="14">
+        <v>340</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>90</v>
+      </c>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>550</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>890</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>49</v>
@@ -1747,21 +1965,31 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="A28" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>120</v>
+      </c>
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>660</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>49</v>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nilesh Yadav\Desktop\daily\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8A08C3-EE79-47C3-86BF-CC957F56B8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC74D0C-B421-4734-84F1-F81160EE652C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>2026=09-11</t>
+  </si>
+  <si>
+    <t>Today was my birthday!!</t>
+  </si>
+  <si>
+    <t>Went Outside for My birthday</t>
   </si>
 </sst>
 </file>
@@ -1708,18 +1714,22 @@
       <c r="E21" s="14">
         <v>180</v>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
       <c r="H21" s="14">
         <v>40</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>770</v>
+        <v>970</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>670</v>
+        <v>470</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>57</v>
@@ -1748,18 +1758,22 @@
       <c r="E22" s="14">
         <v>120</v>
       </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
       <c r="H22" s="14">
         <v>50</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>730</v>
+        <v>1080</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>710</v>
+        <v>360</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>60</v>
@@ -1788,18 +1802,22 @@
       <c r="E23" s="14">
         <v>60</v>
       </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
       <c r="H23" s="14">
         <v>140</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>1230</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>210</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>60</v>
@@ -1828,16 +1846,22 @@
       <c r="E24" s="14">
         <v>80</v>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="F24" s="14">
+        <v>150</v>
+      </c>
+      <c r="G24" s="14">
+        <v>3</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>710</v>
+        <v>980</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>730</v>
+        <v>460</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>49</v>
@@ -1866,16 +1890,22 @@
       <c r="E25" s="14">
         <v>90</v>
       </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
+      <c r="F25" s="14">
+        <v>150</v>
+      </c>
+      <c r="G25" s="14">
+        <v>3</v>
+      </c>
+      <c r="H25" s="14">
+        <v>80</v>
+      </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>680</v>
+        <v>910</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>530</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
@@ -1904,16 +1934,22 @@
       <c r="E26" s="14">
         <v>80</v>
       </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>300</v>
+      </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>770</v>
+        <v>1070</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>670</v>
+        <v>370</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
@@ -1924,7 +1960,9 @@
       <c r="M26" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="17"/>
+      <c r="N26" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
@@ -1942,16 +1980,22 @@
       <c r="E27" s="14">
         <v>90</v>
       </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>400</v>
+      </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>550</v>
+        <v>950</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>890</v>
+        <v>490</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>49</v>
@@ -1962,7 +2006,9 @@
       <c r="M27" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N27" s="17"/>
+      <c r="N27" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
@@ -1980,16 +2026,22 @@
       <c r="E28" s="14">
         <v>120</v>
       </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
+      <c r="F28" s="14">
+        <v>200</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>780</v>
+        <v>1100</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>340</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>49</v>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nilesh Yadav\Desktop\daily\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC74D0C-B421-4734-84F1-F81160EE652C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79B40AA-193A-47D3-BFB0-65C2EA2F1811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -231,9 +231,6 @@
     <t>Nilesh Yadav</t>
   </si>
   <si>
-    <t>CAP776</t>
-  </si>
-  <si>
     <t>August</t>
   </si>
   <si>
@@ -250,6 +247,9 @@
   </si>
   <si>
     <t>Went Outside for My birthday</t>
+  </si>
+  <si>
+    <t>MCA</t>
   </si>
 </sst>
 </file>
@@ -954,7 +954,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -962,7 +962,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1474,7 +1474,7 @@
         <v>54</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1515,7 +1515,7 @@
         <v>55</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B25" s="14">
         <v>380</v>
@@ -1914,7 +1914,7 @@
         <v>60</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N25" s="17"/>
     </row>
@@ -1961,7 +1961,7 @@
         <v>51</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2007,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2055,25 +2055,47 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B29" s="14">
+        <v>180</v>
+      </c>
+      <c r="C29" s="14">
+        <v>50</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>350</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>560</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nilesh Yadav\Desktop\daily\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79B40AA-193A-47D3-BFB0-65C2EA2F1811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C3BD28-13B8-4E75-80E3-2BA6BCAF928C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>MCA</t>
+  </si>
+  <si>
+    <t>feeling low</t>
   </si>
 </sst>
 </file>
@@ -2099,48 +2102,94 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B30" s="14">
+        <v>240</v>
+      </c>
+      <c r="C30" s="14">
+        <v>50</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>130</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>530</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B31" s="14">
+        <v>60</v>
+      </c>
+      <c r="C31" s="14">
+        <v>120</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>120</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>900</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nilesh Yadav\Desktop\daily\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C3BD28-13B8-4E75-80E3-2BA6BCAF928C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CD7335-B89D-4472-936A-938CBA5479F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>feeling low</t>
+  </si>
+  <si>
+    <t>6-</t>
   </si>
 </sst>
 </file>
@@ -1890,8 +1893,8 @@
       <c r="D25" s="14">
         <v>140</v>
       </c>
-      <c r="E25" s="14">
-        <v>90</v>
+      <c r="E25" s="14" t="s">
+        <v>72</v>
       </c>
       <c r="F25" s="14">
         <v>150</v>
@@ -1904,11 +1907,11 @@
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>820</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>620</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
@@ -2192,157 +2195,311 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B32" s="14">
+        <v>480</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>100</v>
+      </c>
+      <c r="E32" s="14">
+        <v>100</v>
+      </c>
+      <c r="F32" s="14">
+        <v>250</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>180</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B33" s="14">
+        <v>480</v>
+      </c>
+      <c r="C33" s="14">
+        <v>50</v>
+      </c>
+      <c r="D33" s="14">
+        <v>180</v>
+      </c>
+      <c r="E33" s="14">
+        <v>50</v>
+      </c>
+      <c r="F33" s="14">
+        <v>50</v>
+      </c>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
+        <v>180</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B34" s="14">
+        <v>480</v>
+      </c>
+      <c r="C34" s="14">
+        <v>50</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>100</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>180</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>50</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>120</v>
+      </c>
+      <c r="F35" s="14">
+        <v>200</v>
+      </c>
+      <c r="G35" s="14">
+        <v>4</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B36" s="14">
+        <v>300</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>180</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B37" s="14">
+        <v>300</v>
+      </c>
+      <c r="C37" s="14">
+        <v>50</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>120</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>180</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>670</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B38" s="14">
+        <v>300</v>
+      </c>
+      <c r="C38" s="14">
+        <v>50</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>120</v>
+      </c>
+      <c r="F38" s="14">
+        <v>150</v>
+      </c>
+      <c r="G38" s="14">
+        <v>3</v>
+      </c>
+      <c r="H38" s="14">
+        <v>180</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nilesh Yadav\Desktop\daily\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CD7335-B89D-4472-936A-938CBA5479F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05350ABC-1CFE-4208-A4EB-D977A8BB19E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2503,25 +2503,47 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B39" s="14">
+        <v>120</v>
+      </c>
+      <c r="C39" s="14">
+        <v>60</v>
+      </c>
+      <c r="D39" s="14">
+        <v>120</v>
+      </c>
+      <c r="E39" s="14">
+        <v>60</v>
+      </c>
+      <c r="F39" s="14">
+        <v>250</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14">
+        <v>180</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
